--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5013-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5013-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D562C365-896E-4881-BC1D-16AA299644E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{87691769-92D7-4268-B8E0-CCBB034A8B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{2CDB7D23-2E5F-494D-8BF6-F66C138DEF8C}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{C788E9A3-E2F2-4E7F-8E99-1E587525E1F7}"/>
   </bookViews>
   <sheets>
     <sheet name="5013-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1577,29 +1577,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE48EA93-9C4E-4CE8-9E9C-EB769D261D20}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{697B3F51-F85F-49E1-832C-EA2B1C39A752}">
   <dimension ref="A1:X42"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1633,7 +1632,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1669,7 +1668,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1721,7 +1720,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1789,7 +1788,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1861,7 +1860,7 @@
         <v>3.11</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1933,7 +1932,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -2005,7 +2004,7 @@
         <v>4.91</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2077,7 +2076,7 @@
         <v>6.39</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2149,7 +2148,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2221,7 +2220,7 @@
         <v>2.42</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2293,7 +2292,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2365,7 +2364,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="41">
         <v>2016</v>
       </c>
@@ -2437,7 +2436,7 @@
         <v>8.27</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="43"/>
       <c r="B14" s="44"/>
       <c r="C14" s="18" t="s">
@@ -2465,7 +2464,7 @@
       <c r="W14" s="50"/>
       <c r="X14" s="46"/>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="39">
         <v>2015</v>
       </c>
@@ -2537,7 +2536,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="41">
         <v>2014</v>
       </c>
@@ -2609,7 +2608,7 @@
         <v>8.9600000000000009</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="43"/>
       <c r="B17" s="44"/>
       <c r="C17" s="18" t="s">
@@ -2637,7 +2636,7 @@
       <c r="W17" s="50"/>
       <c r="X17" s="46"/>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="51">
         <v>2013</v>
       </c>
@@ -2709,7 +2708,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="53"/>
       <c r="B19" s="54"/>
       <c r="C19" s="20" t="s">
@@ -2737,7 +2736,7 @@
       <c r="W19" s="60"/>
       <c r="X19" s="56"/>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2012</v>
       </c>
@@ -2809,7 +2808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="51">
         <v>2011</v>
       </c>
@@ -2881,7 +2880,7 @@
         <v>6.57</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="53"/>
       <c r="B22" s="54"/>
       <c r="C22" s="20" t="s">
@@ -2909,7 +2908,7 @@
       <c r="W22" s="60"/>
       <c r="X22" s="56"/>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2010</v>
       </c>
@@ -2981,7 +2980,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>2009</v>
       </c>
@@ -3053,7 +3052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2008</v>
       </c>
@@ -3125,7 +3124,7 @@
         <v>7.52</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="51">
         <v>2007</v>
       </c>
@@ -3197,7 +3196,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="53"/>
       <c r="B27" s="54"/>
       <c r="C27" s="20" t="s">
@@ -3225,7 +3224,7 @@
       <c r="W27" s="60"/>
       <c r="X27" s="56"/>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="41">
         <v>2006</v>
       </c>
@@ -3297,7 +3296,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="43"/>
       <c r="B29" s="44"/>
       <c r="C29" s="18" t="s">
@@ -3325,7 +3324,7 @@
       <c r="W29" s="50"/>
       <c r="X29" s="46"/>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="51">
         <v>2005</v>
       </c>
@@ -3397,7 +3396,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="53"/>
       <c r="B31" s="54"/>
       <c r="C31" s="20" t="s">
@@ -3425,7 +3424,7 @@
       <c r="W31" s="60"/>
       <c r="X31" s="56"/>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="41">
         <v>2004</v>
       </c>
@@ -3497,7 +3496,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="43"/>
       <c r="B33" s="44"/>
       <c r="C33" s="18" t="s">
@@ -3525,7 +3524,7 @@
       <c r="W33" s="50"/>
       <c r="X33" s="46"/>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>2003</v>
       </c>
@@ -3597,7 +3596,7 @@
         <v>9.49</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>2002</v>
       </c>
@@ -3669,7 +3668,7 @@
         <v>8.39</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="39">
         <v>2001</v>
       </c>
@@ -3741,7 +3740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>2000</v>
       </c>
@@ -3813,7 +3812,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="39">
         <v>1999</v>
       </c>
@@ -3885,7 +3884,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>1998</v>
       </c>
@@ -3957,7 +3956,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="39">
         <v>1997</v>
       </c>
@@ -4029,7 +4028,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>1996</v>
       </c>
@@ -4101,7 +4100,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="39" t="s">
         <v>61</v>
       </c>
